--- a/StructureDefinition-openimis-insurance-organization.xlsx
+++ b/StructureDefinition-openimis-insurance-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-26T15:39:34+00:00</t>
+    <t>2025-09-08T11:14:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5978,7 +5978,7 @@
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>22</v>
@@ -7628,7 +7628,7 @@
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>22</v>
@@ -8681,7 +8681,7 @@
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>22</v>
@@ -8919,7 +8919,7 @@
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>22</v>
@@ -9036,7 +9036,7 @@
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>22</v>
@@ -9153,7 +9153,7 @@
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>22</v>
@@ -9268,7 +9268,7 @@
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>22</v>
@@ -9383,7 +9383,7 @@
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>22</v>
@@ -14513,7 +14513,7 @@
         <v>80</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>22</v>
@@ -14628,7 +14628,7 @@
         <v>80</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>22</v>
@@ -15096,7 +15096,7 @@
         <v>80</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>22</v>

--- a/StructureDefinition-openimis-insurance-organization.xlsx
+++ b/StructureDefinition-openimis-insurance-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:14:40+00:00</t>
+    <t>2025-09-08T11:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-openimis-insurance-organization.xlsx
+++ b/StructureDefinition-openimis-insurance-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:37:47+00:00</t>
+    <t>2025-09-08T11:49:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
